--- a/sus-preferences.xlsx
+++ b/sus-preferences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timogafner/tmp/minizinc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timogafner/Documents/dev.data/Projects/optimized-distribution/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2351E05-9EBC-3F4B-B056-EA0EB885FA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0E730C-67D6-3749-BD92-68B34F4C20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{163794C6-936F-184B-A27A-56381F58B4AF}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Buckets" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -345,18 +345,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,240 +1171,240 @@
   <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.33203125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="12" customWidth="1"/>
-    <col min="5" max="7" width="10.83203125" style="11" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" style="10"/>
-    <col min="9" max="9" width="10.83203125" style="11"/>
-    <col min="10" max="10" width="10.83203125" style="12"/>
-    <col min="11" max="12" width="10.83203125" style="11"/>
-    <col min="13" max="13" width="10.83203125" style="12"/>
+    <col min="2" max="2" width="9.33203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="8" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="9" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="7"/>
+    <col min="9" max="9" width="10.83203125" style="8"/>
+    <col min="10" max="10" width="10.83203125" style="9"/>
+    <col min="11" max="12" width="10.83203125" style="8"/>
+    <col min="13" max="13" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="7">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="8">
-        <v>2</v>
-      </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="7">
-        <v>3</v>
-      </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="7">
-        <v>4</v>
-      </c>
-      <c r="L1" s="8"/>
-      <c r="M1" s="9"/>
+      <c r="B1" s="11">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="10">
+        <v>2</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11">
+        <v>3</v>
+      </c>
+      <c r="I1" s="10"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="11">
+        <v>4</v>
+      </c>
+      <c r="L1" s="10"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
-      <c r="B2" s="10" t="str" cm="1">
+      <c r="B2" s="7" t="str" cm="1">
         <f t="array" ref="B2:D3">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=B$1)</f>
         <v>009</v>
       </c>
-      <c r="C2" s="11" t="str">
+      <c r="C2" s="8" t="str">
         <v>Lea</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="9" t="str">
         <v>Ford</v>
       </c>
-      <c r="E2" s="11" t="str" cm="1">
+      <c r="E2" s="8" t="str" cm="1">
         <f t="array" ref="E2:G9">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=E$1)</f>
         <v>001</v>
       </c>
-      <c r="F2" s="11" t="str">
+      <c r="F2" s="8" t="str">
         <v>Max</v>
       </c>
-      <c r="G2" s="11" t="str">
+      <c r="G2" s="8" t="str">
         <v>Miller</v>
       </c>
-      <c r="H2" s="10" t="str" cm="1">
+      <c r="H2" s="7" t="str" cm="1">
         <f t="array" ref="H2:J7">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=H$1)</f>
         <v>011</v>
       </c>
-      <c r="I2" s="11" t="str">
+      <c r="I2" s="8" t="str">
         <v>Anna</v>
       </c>
-      <c r="J2" s="12" t="str">
+      <c r="J2" s="9" t="str">
         <v>Ford</v>
       </c>
-      <c r="K2" s="11" t="str" cm="1">
+      <c r="K2" s="8" t="str" cm="1">
         <f t="array" ref="K2:M5">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=K$1)</f>
         <v>017</v>
       </c>
-      <c r="L2" s="11" t="str">
+      <c r="L2" s="8" t="str">
         <v>Joana</v>
       </c>
-      <c r="M2" s="12" t="str">
+      <c r="M2" s="9" t="str">
         <v>Ford</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="str">
+      <c r="B3" s="7" t="str">
         <v>010</v>
       </c>
-      <c r="C3" s="11" t="str">
+      <c r="C3" s="8" t="str">
         <v>Max</v>
       </c>
-      <c r="D3" s="12" t="str">
+      <c r="D3" s="9" t="str">
         <v>Clooney</v>
       </c>
-      <c r="E3" s="11" t="str">
+      <c r="E3" s="8" t="str">
         <v>002</v>
       </c>
-      <c r="F3" s="11" t="str">
+      <c r="F3" s="8" t="str">
         <v>Anna</v>
       </c>
-      <c r="G3" s="11" t="str">
+      <c r="G3" s="8" t="str">
         <v>Miles</v>
       </c>
-      <c r="H3" s="10" t="str">
+      <c r="H3" s="7" t="str">
         <v>012</v>
       </c>
-      <c r="I3" s="11" t="str">
+      <c r="I3" s="8" t="str">
         <v>John</v>
       </c>
-      <c r="J3" s="12" t="str">
+      <c r="J3" s="9" t="str">
         <v>Meyers</v>
       </c>
-      <c r="K3" s="11" t="str">
+      <c r="K3" s="8" t="str">
         <v>018</v>
       </c>
-      <c r="L3" s="11" t="str">
+      <c r="L3" s="8" t="str">
         <v>Lea</v>
       </c>
-      <c r="M3" s="12" t="str">
+      <c r="M3" s="9" t="str">
         <v>Meyers</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E4" s="11" t="str">
+      <c r="E4" s="8" t="str">
         <v>003</v>
       </c>
-      <c r="F4" s="11" t="str">
+      <c r="F4" s="8" t="str">
         <v>John</v>
       </c>
-      <c r="G4" s="11" t="str">
+      <c r="G4" s="8" t="str">
         <v>Ford</v>
       </c>
-      <c r="H4" s="10" t="str">
+      <c r="H4" s="7" t="str">
         <v>013</v>
       </c>
-      <c r="I4" s="11" t="str">
+      <c r="I4" s="8" t="str">
         <v>Brad</v>
       </c>
-      <c r="J4" s="12" t="str">
+      <c r="J4" s="9" t="str">
         <v>Miller</v>
       </c>
-      <c r="K4" s="11" t="str">
+      <c r="K4" s="8" t="str">
         <v>019</v>
       </c>
-      <c r="L4" s="11" t="str">
+      <c r="L4" s="8" t="str">
         <v>Max</v>
       </c>
-      <c r="M4" s="12" t="str">
+      <c r="M4" s="9" t="str">
         <v>Miller</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E5" s="11" t="str">
+      <c r="E5" s="8" t="str">
         <v>004</v>
       </c>
-      <c r="F5" s="11" t="str">
+      <c r="F5" s="8" t="str">
         <v>Brad</v>
       </c>
-      <c r="G5" s="11" t="str">
+      <c r="G5" s="8" t="str">
         <v>Clooney</v>
       </c>
-      <c r="H5" s="10" t="str">
+      <c r="H5" s="7" t="str">
         <v>014</v>
       </c>
-      <c r="I5" s="11" t="str">
+      <c r="I5" s="8" t="str">
         <v>Tom</v>
       </c>
-      <c r="J5" s="12" t="str">
+      <c r="J5" s="9" t="str">
         <v>Floyd</v>
       </c>
-      <c r="K5" s="11" t="str">
+      <c r="K5" s="8" t="str">
         <v>020</v>
       </c>
-      <c r="L5" s="11" t="str">
+      <c r="L5" s="8" t="str">
         <v>Anna</v>
       </c>
-      <c r="M5" s="12" t="str">
+      <c r="M5" s="9" t="str">
         <v>Miles</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E6" s="11" t="str">
+      <c r="E6" s="8" t="str">
         <v>005</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="F6" s="8" t="str">
         <v>Tom</v>
       </c>
-      <c r="G6" s="11" t="str">
+      <c r="G6" s="8" t="str">
         <v>Ford</v>
       </c>
-      <c r="H6" s="10" t="str">
+      <c r="H6" s="7" t="str">
         <v>015</v>
       </c>
-      <c r="I6" s="11" t="str">
+      <c r="I6" s="8" t="str">
         <v>Mike</v>
       </c>
-      <c r="J6" s="12" t="str">
+      <c r="J6" s="9" t="str">
         <v>Ford</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E7" s="11" t="str">
+      <c r="E7" s="8" t="str">
         <v>006</v>
       </c>
-      <c r="F7" s="11" t="str">
+      <c r="F7" s="8" t="str">
         <v>Mike</v>
       </c>
-      <c r="G7" s="11" t="str">
+      <c r="G7" s="8" t="str">
         <v>Meyers</v>
       </c>
-      <c r="H7" s="10" t="str">
+      <c r="H7" s="7" t="str">
         <v>016</v>
       </c>
-      <c r="I7" s="11" t="str">
+      <c r="I7" s="8" t="str">
         <v>Michele</v>
       </c>
-      <c r="J7" s="12" t="str">
+      <c r="J7" s="9" t="str">
         <v>Clooney</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E8" s="11" t="str">
+      <c r="E8" s="8" t="str">
         <v>007</v>
       </c>
-      <c r="F8" s="11" t="str">
+      <c r="F8" s="8" t="str">
         <v>Michele</v>
       </c>
-      <c r="G8" s="11" t="str">
+      <c r="G8" s="8" t="str">
         <v>Miller</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E9" s="11" t="str">
+      <c r="E9" s="8" t="str">
         <v>008</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="8" t="str">
         <v>Joana</v>
       </c>
-      <c r="G9" s="11" t="str">
+      <c r="G9" s="8" t="str">
         <v>Miles</v>
       </c>
     </row>

--- a/sus-preferences.xlsx
+++ b/sus-preferences.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timogafner/Documents/dev.data/Projects/optimized-distribution/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0E730C-67D6-3749-BD92-68B34F4C20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90370279-3C1D-1B40-90BF-4C857F77FCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{163794C6-936F-184B-A27A-56381F58B4AF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -184,10 +184,10 @@
     <t>Floyd</t>
   </si>
   <si>
-    <t>ASSIGNED BUCKET</t>
-  </si>
-  <si>
     <t>BUCKET</t>
+  </si>
+  <si>
+    <t>priority 4</t>
   </si>
 </sst>
 </file>
@@ -671,11 +671,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{707EDA64-3523-F744-811A-FC0D2AFF7086}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -698,7 +697,7 @@
         <v>22</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -712,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -744,7 +743,7 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -767,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -790,7 +789,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -813,7 +812,7 @@
         <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -836,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -859,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -882,7 +881,7 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -905,7 +904,7 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -928,7 +927,7 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -951,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -974,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -997,7 +996,7 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1020,7 +1019,7 @@
         <v>4</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1043,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1066,7 +1065,7 @@
         <v>3</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1089,41 +1088,18 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1135,30 +1111,53 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>16</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21">
-        <v>4</v>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1168,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96616689-B52A-054C-B474-2A8065C77896}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.33203125" style="7" customWidth="1"/>
@@ -1184,7 +1183,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="11">
         <v>1</v>
@@ -1209,203 +1208,21 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
-      <c r="B2" s="7" t="str" cm="1">
-        <f t="array" ref="B2:D3">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=B$1)</f>
-        <v>009</v>
-      </c>
-      <c r="C2" s="8" t="str">
-        <v>Lea</v>
-      </c>
-      <c r="D2" s="9" t="str">
-        <v>Ford</v>
-      </c>
-      <c r="E2" s="8" t="str" cm="1">
-        <f t="array" ref="E2:G9">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=E$1)</f>
-        <v>001</v>
-      </c>
-      <c r="F2" s="8" t="str">
-        <v>Max</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <v>Miller</v>
-      </c>
-      <c r="H2" s="7" t="str" cm="1">
-        <f t="array" ref="H2:J7">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=H$1)</f>
-        <v>011</v>
-      </c>
-      <c r="I2" s="8" t="str">
-        <v>Anna</v>
-      </c>
-      <c r="J2" s="9" t="str">
-        <v>Ford</v>
-      </c>
-      <c r="K2" s="8" t="str" cm="1">
-        <f t="array" ref="K2:M5">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!$G:$G=K$1)</f>
-        <v>017</v>
-      </c>
-      <c r="L2" s="8" t="str">
-        <v>Joana</v>
-      </c>
-      <c r="M2" s="9" t="str">
-        <v>Ford</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="7" t="str">
-        <v>010</v>
-      </c>
-      <c r="C3" s="8" t="str">
-        <v>Max</v>
-      </c>
-      <c r="D3" s="9" t="str">
-        <v>Clooney</v>
-      </c>
-      <c r="E3" s="8" t="str">
-        <v>002</v>
-      </c>
-      <c r="F3" s="8" t="str">
-        <v>Anna</v>
-      </c>
-      <c r="G3" s="8" t="str">
-        <v>Miles</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <v>012</v>
-      </c>
-      <c r="I3" s="8" t="str">
-        <v>John</v>
-      </c>
-      <c r="J3" s="9" t="str">
-        <v>Meyers</v>
-      </c>
-      <c r="K3" s="8" t="str">
-        <v>018</v>
-      </c>
-      <c r="L3" s="8" t="str">
-        <v>Lea</v>
-      </c>
-      <c r="M3" s="9" t="str">
-        <v>Meyers</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E4" s="8" t="str">
-        <v>003</v>
-      </c>
-      <c r="F4" s="8" t="str">
-        <v>John</v>
-      </c>
-      <c r="G4" s="8" t="str">
-        <v>Ford</v>
-      </c>
-      <c r="H4" s="7" t="str">
-        <v>013</v>
-      </c>
-      <c r="I4" s="8" t="str">
-        <v>Brad</v>
-      </c>
-      <c r="J4" s="9" t="str">
-        <v>Miller</v>
-      </c>
-      <c r="K4" s="8" t="str">
-        <v>019</v>
-      </c>
-      <c r="L4" s="8" t="str">
-        <v>Max</v>
-      </c>
-      <c r="M4" s="9" t="str">
-        <v>Miller</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E5" s="8" t="str">
-        <v>004</v>
-      </c>
-      <c r="F5" s="8" t="str">
-        <v>Brad</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <v>Clooney</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <v>014</v>
-      </c>
-      <c r="I5" s="8" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="J5" s="9" t="str">
-        <v>Floyd</v>
-      </c>
-      <c r="K5" s="8" t="str">
-        <v>020</v>
-      </c>
-      <c r="L5" s="8" t="str">
-        <v>Anna</v>
-      </c>
-      <c r="M5" s="9" t="str">
-        <v>Miles</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E6" s="8" t="str">
-        <v>005</v>
-      </c>
-      <c r="F6" s="8" t="str">
-        <v>Tom</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <v>Ford</v>
-      </c>
-      <c r="H6" s="7" t="str">
-        <v>015</v>
-      </c>
-      <c r="I6" s="8" t="str">
-        <v>Mike</v>
-      </c>
-      <c r="J6" s="9" t="str">
-        <v>Ford</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E7" s="8" t="str">
-        <v>006</v>
-      </c>
-      <c r="F7" s="8" t="str">
-        <v>Mike</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <v>Meyers</v>
-      </c>
-      <c r="H7" s="7" t="str">
-        <v>016</v>
-      </c>
-      <c r="I7" s="8" t="str">
-        <v>Michele</v>
-      </c>
-      <c r="J7" s="9" t="str">
-        <v>Clooney</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E8" s="8" t="str">
-        <v>007</v>
-      </c>
-      <c r="F8" s="8" t="str">
-        <v>Michele</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <v>Miller</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="E9" s="8" t="str">
-        <v>008</v>
-      </c>
-      <c r="F9" s="8" t="str">
-        <v>Joana</v>
-      </c>
-      <c r="G9" s="8" t="str">
-        <v>Miles</v>
+      <c r="B2" s="7" t="e" cm="1">
+        <f t="array" ref="B2">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!#REF!=B$1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E2" s="8" t="e" cm="1">
+        <f t="array" ref="E2">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!#REF!=E$1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H2" s="7" t="e" cm="1">
+        <f t="array" ref="H2">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!#REF!=H$1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="K2" s="8" t="e" cm="1">
+        <f t="array" ref="K2">_xlfn._xlws.FILTER(Sheet1!$A:$C,Sheet1!#REF!=K$1)</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
